--- a/Специальности/РПО_Разработка_ПО/02_Тематический_план/Тематический_план_ИКТ_РПО.xlsx
+++ b/Специальности/РПО_Разработка_ПО/02_Тематический_план/Тематический_план_ИКТ_РПО.xlsx
@@ -1,30 +1,42 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniy\Documents\Работа с Claud.Ai\ВСе для ИКТ\Специальности\РПО_Разработка_ПО\02_Тематический_план\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCBBC9AC-BB15-48F0-9AB7-62249E51C36F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="13800" xr2:uid="{1835FFBE-C7E4-448C-9C04-5668B6BB9FBA}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="ИКТ РПО" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Листы</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>ИКТ РПО</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <Company/>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>Daniyar Kaliaskarov</dc:creator>
+  <cp:lastModifiedBy>Daniyar Kaliaskarov</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-06-20T05:58:58Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-06-20T05:59:01Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="111">
   <si>
     <t>Тематический план модуля «Применение ИКТ и цифровых технологий» — РПО (4S06130103). 96 ч / 4 кр, 3 семестр, зачёт. СРС 72 ч.</t>
@@ -362,7 +374,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -506,7 +518,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
     <a:clrScheme name="Стандартная">
@@ -801,7 +813,32 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniy\Documents\Работа с Claud.Ai\ВСе для ИКТ\Специальности\РПО_Разработка_ПО\02_Тематический_план\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCBBC9AC-BB15-48F0-9AB7-62249E51C36F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13800" windowHeight="13800" xr2:uid="{1835FFBE-C7E4-448C-9C04-5668B6BB9FBA}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="ИКТ РПО" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F75DD74-6D92-4670-9C37-F8DFE08F2692}">
   <dimension ref="A1:L48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -904,9 +941,6 @@
       <c r="E4" s="11">
         <v>2</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
       <c r="I4" s="11">
         <v>2</v>
       </c>
@@ -936,9 +970,6 @@
       <c r="E5" s="11">
         <v>2</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
       <c r="I5" s="11">
         <v>2</v>
       </c>
@@ -965,17 +996,19 @@
       <c r="D6" s="11">
         <v>2</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
       <c r="F6" s="11">
-        <v>2</v>
-      </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I6" s="11">
         <v>2</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>22</v>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -1000,8 +1033,6 @@
       <c r="E7" s="11">
         <v>1</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
       <c r="H7" s="11">
         <v>1</v>
       </c>
@@ -1031,11 +1062,9 @@
       <c r="D8" s="11">
         <v>2</v>
       </c>
-      <c r="E8" s="11"/>
       <c r="F8" s="11">
         <v>1</v>
       </c>
-      <c r="G8" s="11"/>
       <c r="H8" s="11">
         <v>1</v>
       </c>
@@ -1065,11 +1094,9 @@
       <c r="D9" s="11">
         <v>2</v>
       </c>
-      <c r="E9" s="11"/>
       <c r="F9" s="11">
         <v>1</v>
       </c>
-      <c r="G9" s="11"/>
       <c r="H9" s="11">
         <v>1</v>
       </c>
@@ -1099,11 +1126,9 @@
       <c r="D10" s="11">
         <v>2</v>
       </c>
-      <c r="E10" s="11"/>
       <c r="F10" s="11">
         <v>1</v>
       </c>
-      <c r="G10" s="11"/>
       <c r="H10" s="11">
         <v>1</v>
       </c>
@@ -1139,8 +1164,6 @@
       <c r="F11" s="11">
         <v>1</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
       <c r="I11" s="11">
         <v>2</v>
       </c>
@@ -1165,11 +1188,9 @@
       <c r="D12" s="11">
         <v>2</v>
       </c>
-      <c r="E12" s="11"/>
       <c r="F12" s="11">
         <v>1</v>
       </c>
-      <c r="G12" s="11"/>
       <c r="H12" s="11">
         <v>1</v>
       </c>
@@ -1200,9 +1221,6 @@
       <c r="E13" s="11">
         <v>2</v>
       </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
       <c r="I13" s="11">
         <v>2</v>
       </c>
@@ -1227,11 +1245,9 @@
       <c r="D14" s="11">
         <v>2</v>
       </c>
-      <c r="E14" s="11"/>
       <c r="F14" s="11">
         <v>1</v>
       </c>
-      <c r="G14" s="11"/>
       <c r="H14" s="11">
         <v>1</v>
       </c>
@@ -1261,17 +1277,19 @@
       <c r="D15" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="11">
+        <v>1</v>
+      </c>
       <c r="F15" s="11">
-        <v>2</v>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I15" s="11">
         <v>2</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>22</v>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K15" s="7" t="s">
         <v>45</v>
@@ -1312,9 +1330,6 @@
       <c r="E17" s="11">
         <v>2</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
       <c r="I17" s="11">
         <v>2</v>
       </c>
@@ -1339,11 +1354,9 @@
       <c r="D18" s="11">
         <v>2</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11">
-        <v>1</v>
-      </c>
-      <c r="G18" s="11"/>
+      <c r="E18" s="11">
+        <v>1</v>
+      </c>
       <c r="H18" s="11">
         <v>1</v>
       </c>
@@ -1371,17 +1384,19 @@
       <c r="D19" s="11">
         <v>2</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="11">
+        <v>1</v>
+      </c>
       <c r="F19" s="11">
-        <v>2</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I19" s="11">
         <v>2</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>22</v>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K19" s="7" t="s">
         <v>52</v>
@@ -1401,17 +1416,19 @@
       <c r="D20" s="11">
         <v>2</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
       <c r="F20" s="11">
-        <v>2</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I20" s="11">
         <v>2</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>22</v>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K20" s="7" t="s">
         <v>54</v>
@@ -1433,17 +1450,19 @@
       <c r="D21" s="11">
         <v>2</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="11">
+        <v>1</v>
+      </c>
       <c r="F21" s="11">
-        <v>2</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I21" s="11">
         <v>2</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>22</v>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K21" s="7" t="s">
         <v>56</v>
@@ -1463,11 +1482,9 @@
       <c r="D22" s="11">
         <v>2</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="G22" s="11"/>
+      <c r="E22" s="11">
+        <v>1</v>
+      </c>
       <c r="H22" s="11">
         <v>1</v>
       </c>
@@ -1495,17 +1512,19 @@
       <c r="D23" s="11">
         <v>2</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
       <c r="F23" s="11">
-        <v>2</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I23" s="11">
         <v>2</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>22</v>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K23" s="7" t="s">
         <v>60</v>
@@ -1533,8 +1552,6 @@
       <c r="F24" s="11">
         <v>1</v>
       </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
       <c r="I24" s="11">
         <v>2</v>
       </c>
@@ -1561,11 +1578,9 @@
       <c r="D25" s="11">
         <v>2</v>
       </c>
-      <c r="E25" s="11"/>
       <c r="F25" s="11">
         <v>1</v>
       </c>
-      <c r="G25" s="11"/>
       <c r="H25" s="11">
         <v>1</v>
       </c>
@@ -1593,11 +1608,9 @@
       <c r="D26" s="11">
         <v>2</v>
       </c>
-      <c r="E26" s="11"/>
       <c r="F26" s="11">
         <v>1</v>
       </c>
-      <c r="G26" s="11"/>
       <c r="H26" s="11">
         <v>1</v>
       </c>
@@ -1625,17 +1638,19 @@
       <c r="D27" s="11">
         <v>2</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11">
-        <v>2</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
+      <c r="E27" s="11">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11">
+        <v>1</v>
+      </c>
       <c r="I27" s="11">
         <v>2</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>22</v>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K27" s="7" t="s">
         <v>69</v>
@@ -1655,11 +1670,9 @@
       <c r="D28" s="11">
         <v>2</v>
       </c>
-      <c r="E28" s="11"/>
       <c r="F28" s="11">
         <v>1</v>
       </c>
-      <c r="G28" s="11"/>
       <c r="H28" s="11">
         <v>1</v>
       </c>
@@ -1706,9 +1719,6 @@
       <c r="E30" s="11">
         <v>2</v>
       </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
       <c r="I30" s="11">
         <v>2</v>
       </c>
@@ -1735,19 +1745,22 @@
       <c r="D31" s="11">
         <v>6</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="11">
+        <v>2</v>
+      </c>
       <c r="F31" s="11">
-        <v>5</v>
-      </c>
-      <c r="G31" s="11"/>
+        <v>3</v>
+      </c>
       <c r="H31" s="11">
         <v>1</v>
       </c>
       <c r="I31" s="11">
         <v>2</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>22</v>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K31" s="7" t="s">
         <v>77</v>
@@ -1769,19 +1782,22 @@
       <c r="D32" s="11">
         <v>4</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="11">
+        <v>2</v>
+      </c>
       <c r="F32" s="11">
-        <v>3</v>
-      </c>
-      <c r="G32" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H32" s="11">
         <v>1</v>
       </c>
       <c r="I32" s="11">
         <v>2</v>
       </c>
-      <c r="J32" s="7" t="s">
-        <v>22</v>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K32" s="7" t="s">
         <v>80</v>
@@ -1803,19 +1819,22 @@
       <c r="D33" s="11">
         <v>4</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="11">
+        <v>2</v>
+      </c>
       <c r="F33" s="11">
-        <v>3</v>
-      </c>
-      <c r="G33" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H33" s="11">
         <v>1</v>
       </c>
       <c r="I33" s="11">
         <v>2</v>
       </c>
-      <c r="J33" s="7" t="s">
-        <v>22</v>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K33" s="7" t="s">
         <v>82</v>
@@ -1838,20 +1857,21 @@
         <v>6</v>
       </c>
       <c r="E34" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="11">
-        <v>4</v>
-      </c>
-      <c r="G34" s="11"/>
+        <v>3</v>
+      </c>
       <c r="H34" s="11">
         <v>1</v>
       </c>
       <c r="I34" s="11">
         <v>2</v>
       </c>
-      <c r="J34" s="7" t="s">
-        <v>22</v>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K34" s="7" t="s">
         <v>85</v>
@@ -1873,17 +1893,19 @@
       <c r="D35" s="11">
         <v>4</v>
       </c>
-      <c r="E35" s="11"/>
+      <c r="E35" s="11">
+        <v>2</v>
+      </c>
       <c r="F35" s="11">
-        <v>4</v>
-      </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+        <v>2</v>
+      </c>
       <c r="I35" s="11">
         <v>2</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>22</v>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K35" s="7" t="s">
         <v>88</v>
@@ -1905,17 +1927,19 @@
       <c r="D36" s="11">
         <v>2</v>
       </c>
-      <c r="E36" s="11"/>
+      <c r="E36" s="11">
+        <v>1</v>
+      </c>
       <c r="F36" s="11">
-        <v>2</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I36" s="11">
         <v>2</v>
       </c>
-      <c r="J36" s="7" t="s">
-        <v>22</v>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K36" s="7" t="s">
         <v>90</v>
@@ -1937,12 +1961,10 @@
       <c r="D37" s="11">
         <v>2</v>
       </c>
-      <c r="E37" s="11"/>
+      <c r="E37" s="11">
+        <v>1</v>
+      </c>
       <c r="F37" s="11">
-        <v>1</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11">
         <v>1</v>
       </c>
       <c r="I37" s="11">
@@ -1971,12 +1993,12 @@
       <c r="D38" s="11">
         <v>2</v>
       </c>
-      <c r="E38" s="11"/>
+      <c r="E38" s="11">
+        <v>1</v>
+      </c>
       <c r="F38" s="11">
-        <v>2</v>
-      </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
+        <v>1</v>
+      </c>
       <c r="I38" s="11">
         <v>2</v>
       </c>
@@ -2004,12 +2026,11 @@
         <v>4</v>
       </c>
       <c r="E39" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="11">
-        <v>2</v>
-      </c>
-      <c r="G39" s="11"/>
+        <v>1</v>
+      </c>
       <c r="H39" s="11">
         <v>1</v>
       </c>
@@ -2039,19 +2060,22 @@
       <c r="D40" s="11">
         <v>4</v>
       </c>
-      <c r="E40" s="11"/>
+      <c r="E40" s="11">
+        <v>1</v>
+      </c>
       <c r="F40" s="11">
-        <v>3</v>
-      </c>
-      <c r="G40" s="11"/>
+        <v>2</v>
+      </c>
       <c r="H40" s="11">
         <v>1</v>
       </c>
       <c r="I40" s="11">
         <v>2</v>
       </c>
-      <c r="J40" s="7" t="s">
-        <v>22</v>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Комбинир.</t>
+        </is>
       </c>
       <c r="K40" s="7" t="s">
         <v>99</v>
@@ -2076,9 +2100,6 @@
       <c r="E41" s="11">
         <v>2</v>
       </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
       <c r="I41" s="11">
         <v>2</v>
       </c>
@@ -2106,9 +2127,6 @@
       <c r="E42" s="11">
         <v>2</v>
       </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
       <c r="I42" s="11"/>
       <c r="J42" s="7" t="s">
         <v>15</v>
@@ -2129,12 +2147,9 @@
       <c r="D43" s="11">
         <v>2</v>
       </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11">
-        <v>2</v>
-      </c>
-      <c r="H43" s="11"/>
+      <c r="F43" s="11">
+        <v>2</v>
+      </c>
       <c r="I43" s="11"/>
       <c r="J43" s="7" t="s">
         <v>105</v>
@@ -2157,12 +2172,9 @@
       <c r="D44" s="11">
         <v>2</v>
       </c>
-      <c r="E44" s="11"/>
       <c r="F44" s="11">
         <v>2</v>
       </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
       <c r="I44" s="11"/>
       <c r="J44" s="7" t="s">
         <v>107</v>
@@ -2182,13 +2194,10 @@
         <v>96</v>
       </c>
       <c r="E45" s="12">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F45" s="12">
-        <v>57</v>
-      </c>
-      <c r="G45" s="12">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H45" s="12">
         <v>18</v>
